--- a/tests/vlaanderen/reference/resultaten/werk/alle groepen/herkomsten/restdag/Pot_totaalproduct_Auto_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/alle groepen/herkomsten/restdag/Pot_totaalproduct_Auto_Fiets.xlsx
@@ -388,13 +388,13 @@
         <v>17524.9025578747</v>
       </c>
       <c r="C2">
-        <v>37410.8669219937</v>
+        <v>37410.96819361215</v>
       </c>
       <c r="D2">
-        <v>72913.72309724981</v>
+        <v>72914.56400249722</v>
       </c>
       <c r="E2">
-        <v>110381.739226258</v>
+        <v>110382.3177082942</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>180259.0863915369</v>
+        <v>180259.5059406447</v>
       </c>
       <c r="C3">
-        <v>335269.4101164092</v>
+        <v>335272.8809505744</v>
       </c>
       <c r="D3">
-        <v>406951.9580411431</v>
+        <v>406961.9797942307</v>
       </c>
       <c r="E3">
-        <v>452762.4076493848</v>
+        <v>452771.6265993729</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>19641.39459355674</v>
+        <v>19641.53184776012</v>
       </c>
       <c r="C4">
-        <v>37309.25327830233</v>
+        <v>37310.73200431461</v>
       </c>
       <c r="D4">
-        <v>59530.81393995077</v>
+        <v>59536.0471296245</v>
       </c>
       <c r="E4">
-        <v>77100.64445790015</v>
+        <v>77103.87128756689</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -456,13 +456,13 @@
         <v>105915.2473489126</v>
       </c>
       <c r="C6">
-        <v>134994.1277142083</v>
+        <v>134994.5854020062</v>
       </c>
       <c r="D6">
-        <v>124241.9419601992</v>
+        <v>124245.4795467387</v>
       </c>
       <c r="E6">
-        <v>101914.7166775866</v>
+        <v>101916.4250316102</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>10982.03599266357</v>
+        <v>10982.14968947148</v>
       </c>
       <c r="C7">
-        <v>22033.83159260813</v>
+        <v>22034.10531314592</v>
       </c>
       <c r="D7">
-        <v>24308.01528049599</v>
+        <v>24309.13744422972</v>
       </c>
       <c r="E7">
-        <v>26486.76564533206</v>
+        <v>26487.83749197675</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>810072.9788328224</v>
+        <v>810087.5240000318</v>
       </c>
       <c r="C9">
-        <v>1302205.555769727</v>
+        <v>1302235.130316577</v>
       </c>
       <c r="D9">
-        <v>1766270.874992366</v>
+        <v>1766611.004188546</v>
       </c>
       <c r="E9">
-        <v>2178160.347173009</v>
+        <v>2178365.62574539</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -558,13 +558,13 @@
         <v>867031.8717991085</v>
       </c>
       <c r="C12">
-        <v>1025243.928626533</v>
+        <v>1036533.483528001</v>
       </c>
       <c r="D12">
-        <v>921437.0399734324</v>
+        <v>929521.8725588211</v>
       </c>
       <c r="E12">
-        <v>712577.8037139757</v>
+        <v>713701.8543330178</v>
       </c>
     </row>
     <row r="13" spans="1:5">
